--- a/templates/чек-лист_акт_шаблон.xlsx
+++ b/templates/чек-лист_акт_шаблон.xlsx
@@ -15,7 +15,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Лист осмотра КЛ заполняем втор'!$7:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">' акт заполняем первым'!$A$1:$I$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">' акт заполняем первым'!$A$1:$I$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Лист осмотра КЛ заполняем втор'!$A$1:$R$20</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -762,7 +762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -918,6 +918,12 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -930,78 +936,93 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1053,34 +1074,40 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="28" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1095,9 +1122,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1161,29 +1185,11 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1684,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I63"/>
+  <dimension ref="B1:I69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
@@ -1709,16 +1715,16 @@
       </c>
     </row>
     <row r="2" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D3" s="29" t="s">
@@ -1728,32 +1734,32 @@
       <c r="F3" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
     </row>
     <row r="5" spans="2:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C6" s="15"/>
@@ -1761,36 +1767,36 @@
       <c r="E6" s="15"/>
     </row>
     <row r="7" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="84"/>
     </row>
     <row r="8" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="75"/>
-      <c r="D8" s="59" t="s">
+      <c r="C8" s="80"/>
+      <c r="D8" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="60"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="87"/>
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="43"/>
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
@@ -1799,52 +1805,52 @@
       <c r="I9" s="45"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="54"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="46"/>
       <c r="E10" s="47"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="109"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="118"/>
     </row>
     <row r="11" spans="2:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="68"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="73"/>
     </row>
     <row r="12" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="69" t="s">
+      <c r="C12" s="58"/>
+      <c r="D12" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="71"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="76"/>
     </row>
     <row r="13" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="86" t="s">
+      <c r="C13" s="89"/>
+      <c r="D13" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="87"/>
+      <c r="E13" s="94"/>
       <c r="F13" s="50">
         <v>0.4</v>
       </c>
@@ -1855,52 +1861,52 @@
       <c r="I13" s="28"/>
     </row>
     <row r="14" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="91" t="s">
+      <c r="C14" s="58"/>
+      <c r="D14" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="92"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="92"/>
-      <c r="I14" s="93"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="94" t="s">
+      <c r="C15" s="66"/>
+      <c r="D15" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="76"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="63"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="90"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="97"/>
     </row>
     <row r="17" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="53"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="85"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="92"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C18" s="15"/>
@@ -1908,343 +1914,343 @@
       <c r="E18" s="15"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="96"/>
+      <c r="C19" s="103"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
     </row>
     <row r="20" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="65" t="str">
+      <c r="B20" s="69" t="str">
         <f>IFERROR(IF([1]Список!$B$2=0,"",[1]Список!$B$2),"")</f>
         <v>Начальник СКС</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="57" t="str">
+      <c r="C20" s="69"/>
+      <c r="D20" s="61" t="str">
         <f>IFERROR(IF([1]Список!$C$2=0,"",[1]Список!$C$2),"")</f>
         <v>Филиал ПАО «Россети Волга» - «УРС» - «ЦПО»</v>
       </c>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="57" t="str">
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="61" t="str">
         <f>IFERROR(IF([1]Список!$D$2=0,"",[1]Список!$D$2),"")</f>
         <v>Захаренко Сергей Александрович</v>
       </c>
-      <c r="I20" s="58"/>
-    </row>
-    <row r="21" spans="2:9" s="141" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="136" t="s">
+      <c r="I20" s="62"/>
+    </row>
+    <row r="21" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="137" t="s">
+      <c r="C21" s="70"/>
+      <c r="D21" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="139"/>
-      <c r="H21" s="137" t="s">
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="I21" s="139"/>
+      <c r="I21" s="64"/>
     </row>
     <row r="22" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="65" t="str">
+      <c r="B22" s="69" t="str">
         <f>IFERROR(IF([1]Список!$B$5=0,"",[1]Список!$B$5),"")</f>
         <v>Представитель собственника</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="57" t="str">
+      <c r="C22" s="69"/>
+      <c r="D22" s="61" t="str">
         <f>IFERROR(IF([1]Список!$C$5=0,"",[1]Список!$C$5),"")</f>
         <v/>
       </c>
-      <c r="E22" s="112"/>
-      <c r="F22" s="112"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="57" t="str">
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="61" t="str">
         <f>IFERROR(IF([1]Список!$D$5=0,"",[1]Список!$D$5),"")</f>
         <v/>
       </c>
-      <c r="I22" s="58"/>
-    </row>
-    <row r="23" spans="2:9" s="141" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="140" t="s">
+      <c r="I22" s="62"/>
+    </row>
+    <row r="23" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="140"/>
-      <c r="D23" s="137" t="s">
+      <c r="C23" s="105"/>
+      <c r="D23" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="138"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="139"/>
-      <c r="H23" s="134" t="s">
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="I23" s="135"/>
+      <c r="I23" s="60"/>
     </row>
     <row r="24" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="65" t="str">
+      <c r="B24" s="69" t="str">
         <f>IFERROR(IF([1]Список!$B$6=0,"",[1]Список!$B$6),"")</f>
         <v/>
       </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="57" t="str">
+      <c r="C24" s="69"/>
+      <c r="D24" s="61" t="str">
         <f>IFERROR(IF([1]Список!$C$6=0,"",[1]Список!$C$6),"")</f>
         <v/>
       </c>
-      <c r="E24" s="112"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="57" t="str">
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="61" t="str">
         <f>IFERROR(IF([1]Список!$D$6=0,"",[1]Список!$D$6),"")</f>
         <v/>
       </c>
-      <c r="I24" s="58"/>
-    </row>
-    <row r="25" spans="2:9" s="141" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="140" t="s">
+      <c r="I24" s="62"/>
+    </row>
+    <row r="25" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="140"/>
-      <c r="D25" s="137" t="s">
+      <c r="C25" s="105"/>
+      <c r="D25" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="134" t="s">
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="135"/>
+      <c r="I25" s="60"/>
     </row>
     <row r="26" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="65" t="str">
+      <c r="B26" s="69" t="str">
         <f>IFERROR(IF([1]Список!$B$7=0,"",[1]Список!$B$7),"")</f>
         <v/>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="57" t="str">
+      <c r="C26" s="69"/>
+      <c r="D26" s="61" t="str">
         <f>IFERROR(IF([1]Список!$C$7=0,"",[1]Список!$C$7),"")</f>
         <v/>
       </c>
-      <c r="E26" s="112"/>
-      <c r="F26" s="112"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="57" t="str">
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="61" t="str">
         <f>IFERROR(IF([1]Список!$D$7=0,"",[1]Список!$D$7),"")</f>
         <v/>
       </c>
-      <c r="I26" s="58"/>
-    </row>
-    <row r="27" spans="2:9" s="141" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="140" t="s">
+      <c r="I26" s="62"/>
+    </row>
+    <row r="27" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="140"/>
-      <c r="D27" s="137" t="s">
+      <c r="C27" s="105"/>
+      <c r="D27" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="138"/>
-      <c r="F27" s="138"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="134" t="s">
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="I27" s="135"/>
+      <c r="I27" s="60"/>
     </row>
     <row r="28" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="65" t="str">
+      <c r="B28" s="69" t="str">
         <f>IFERROR(IF([1]Список!$B$8=0,"",[1]Список!$B$8),"")</f>
         <v/>
       </c>
-      <c r="C28" s="65"/>
-      <c r="D28" s="57" t="str">
+      <c r="C28" s="69"/>
+      <c r="D28" s="61" t="str">
         <f>IFERROR(IF([1]Список!$C$8=0,"",[1]Список!$C$8),"")</f>
         <v/>
       </c>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="57" t="str">
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="61" t="str">
         <f>IFERROR(IF([1]Список!$D$8=0,"",[1]Список!$D$8),"")</f>
         <v/>
       </c>
-      <c r="I28" s="58"/>
-    </row>
-    <row r="29" spans="2:9" s="141" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="140" t="s">
+      <c r="I28" s="62"/>
+    </row>
+    <row r="29" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="140"/>
-      <c r="D29" s="137" t="s">
+      <c r="C29" s="105"/>
+      <c r="D29" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="134" t="s">
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="I29" s="135"/>
+      <c r="I29" s="60"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="I32" s="31" t="s">
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="I38" s="31" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C35" s="100" t="s">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C41" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="100"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="100"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="100"/>
-    </row>
-    <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="97" t="s">
+      <c r="D41" s="107"/>
+      <c r="E41" s="107"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="107"/>
+      <c r="H41" s="107"/>
+      <c r="I41" s="107"/>
+    </row>
+    <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="97" t="s">
+      <c r="C42" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="101" t="s">
+      <c r="D42" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="102"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="97" t="s">
+      <c r="E42" s="110"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="H36" s="97" t="s">
+      <c r="H42" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="97" t="s">
+      <c r="I42" s="104" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="97"/>
-      <c r="C37" s="97"/>
-      <c r="D37" s="104" t="s">
+    <row r="43" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="104"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="105"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="97"/>
-      <c r="H37" s="97"/>
-      <c r="I37" s="97"/>
-    </row>
-    <row r="38" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="19">
+      <c r="E43" s="113"/>
+      <c r="F43" s="114"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+    </row>
+    <row r="44" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="19">
         <v>1</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C44" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="40"/>
-      <c r="E38" s="107"/>
-      <c r="F38" s="107"/>
-      <c r="G38" s="23" t="s">
+      <c r="D44" s="40"/>
+      <c r="E44" s="142"/>
+      <c r="F44" s="143"/>
+      <c r="G44" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="H38" s="41"/>
-      <c r="I38" s="52"/>
-    </row>
-    <row r="39" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="19"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-    </row>
-    <row r="40" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="19"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-    </row>
-    <row r="41" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="19"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
-    </row>
-    <row r="42" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="19"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="21"/>
-    </row>
-    <row r="43" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="19"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="21"/>
-    </row>
-    <row r="44" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="19"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="52"/>
     </row>
     <row r="45" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="19"/>
@@ -2276,74 +2282,77 @@
       <c r="H47" s="20"/>
       <c r="I47" s="21"/>
     </row>
-    <row r="48" spans="2:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="111" t="s">
+    <row r="48" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="19"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="21"/>
+    </row>
+    <row r="49" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="19"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="21"/>
+    </row>
+    <row r="50" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="19"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="21"/>
+    </row>
+    <row r="51" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="19"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="21"/>
+    </row>
+    <row r="52" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="19"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="21"/>
+    </row>
+    <row r="53" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="19"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="21"/>
+    </row>
+    <row r="54" spans="2:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="111"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="100" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" s="100"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="100"/>
-      <c r="F50" s="100"/>
-      <c r="G50" s="100"/>
-      <c r="H50" s="100"/>
-      <c r="I50" s="100"/>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="98"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="98"/>
-      <c r="G51" s="98"/>
-      <c r="H51" s="98"/>
-      <c r="I51" s="98"/>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="98"/>
-      <c r="C52" s="98"/>
-      <c r="D52" s="98"/>
-      <c r="E52" s="98"/>
-      <c r="F52" s="98"/>
-      <c r="G52" s="98"/>
-      <c r="H52" s="98"/>
-      <c r="I52" s="98"/>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="98"/>
-      <c r="C53" s="98"/>
-      <c r="D53" s="98"/>
-      <c r="E53" s="98"/>
-      <c r="F53" s="98"/>
-      <c r="G53" s="98"/>
-      <c r="H53" s="98"/>
-      <c r="I53" s="98"/>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="98"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="98"/>
-      <c r="E54" s="98"/>
-      <c r="F54" s="98"/>
-      <c r="G54" s="98"/>
-      <c r="H54" s="98"/>
-      <c r="I54" s="98"/>
+      <c r="C54" s="120"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="120"/>
+      <c r="H54" s="120"/>
+      <c r="I54" s="120"/>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C55" s="17"/>
@@ -2351,161 +2360,218 @@
       <c r="E55" s="17"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="100" t="s">
+      <c r="B56" s="107" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="107"/>
+      <c r="D56" s="107"/>
+      <c r="E56" s="107"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="107"/>
+      <c r="H56" s="107"/>
+      <c r="I56" s="107"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B57" s="108"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="108"/>
+      <c r="E57" s="108"/>
+      <c r="F57" s="108"/>
+      <c r="G57" s="108"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B58" s="108"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="108"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="108"/>
+      <c r="G58" s="108"/>
+      <c r="H58" s="108"/>
+      <c r="I58" s="108"/>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B59" s="108"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="108"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="108"/>
+      <c r="G59" s="108"/>
+      <c r="H59" s="108"/>
+      <c r="I59" s="108"/>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="108"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B62" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="100"/>
-      <c r="D56" s="100"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="100"/>
-      <c r="G56" s="100"/>
-      <c r="H56" s="100"/>
-      <c r="I56" s="100"/>
-    </row>
-    <row r="57" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="97" t="s">
+      <c r="C62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107"/>
+    </row>
+    <row r="63" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="C57" s="97"/>
-      <c r="D57" s="97"/>
-      <c r="E57" s="97" t="s">
+      <c r="C63" s="104"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="F57" s="97"/>
-      <c r="G57" s="97"/>
-      <c r="H57" s="97" t="s">
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="I57" s="97"/>
-    </row>
-    <row r="58" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="99" t="str">
+      <c r="I63" s="104"/>
+    </row>
+    <row r="64" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="106" t="str">
         <f>IFERROR(LEFT(H20,FIND(" ",H20)-1),H20)&amp;IFERROR(" "&amp;MID(H20,FIND(" ",H20)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H20,FIND(" ",H20,FIND(" ",H20)+1)+1,1)&amp;".","")</f>
         <v>Захаренко С. А.</v>
       </c>
-      <c r="C58" s="99"/>
-      <c r="D58" s="99"/>
-      <c r="E58" s="97"/>
-      <c r="F58" s="97"/>
-      <c r="G58" s="97"/>
-      <c r="H58" s="97"/>
-      <c r="I58" s="97"/>
-    </row>
-    <row r="59" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="99" t="str">
+      <c r="C64" s="106"/>
+      <c r="D64" s="106"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="104"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+    </row>
+    <row r="65" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="106" t="str">
         <f>IFERROR(LEFT(H22,FIND(" ",H22)-1),H22)&amp;IFERROR(" "&amp;MID(H22,FIND(" ",H22)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H22,FIND(" ",H22,FIND(" ",H22)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C59" s="99"/>
-      <c r="D59" s="99"/>
-      <c r="E59" s="97"/>
-      <c r="F59" s="97"/>
-      <c r="G59" s="97"/>
-      <c r="H59" s="97"/>
-      <c r="I59" s="97"/>
-    </row>
-    <row r="60" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="99" t="str">
+      <c r="C65" s="106"/>
+      <c r="D65" s="106"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
+      <c r="I65" s="104"/>
+    </row>
+    <row r="66" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="106" t="str">
         <f>IFERROR(LEFT(H24,FIND(" ",H24)-1),H24)&amp;IFERROR(" "&amp;MID(H24,FIND(" ",H24)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H24,FIND(" ",H24,FIND(" ",H24)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C60" s="99"/>
-      <c r="D60" s="99"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-    </row>
-    <row r="61" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="99" t="str">
+      <c r="C66" s="106"/>
+      <c r="D66" s="106"/>
+      <c r="E66" s="104"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="104"/>
+    </row>
+    <row r="67" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="106" t="str">
         <f>IFERROR(LEFT(H26,FIND(" ",H26)-1),H26)&amp;IFERROR(" "&amp;MID(H26,FIND(" ",H26)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H26,FIND(" ",H26,FIND(" ",H26)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C61" s="99"/>
-      <c r="D61" s="99"/>
-      <c r="E61" s="97"/>
-      <c r="F61" s="97"/>
-      <c r="G61" s="97"/>
-      <c r="H61" s="97"/>
-      <c r="I61" s="97"/>
-    </row>
-    <row r="62" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="99" t="str">
+      <c r="C67" s="106"/>
+      <c r="D67" s="106"/>
+      <c r="E67" s="104"/>
+      <c r="F67" s="104"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="104"/>
+      <c r="I67" s="104"/>
+    </row>
+    <row r="68" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="106" t="str">
         <f>IFERROR(LEFT(H28,FIND(" ",H28)-1),H28)&amp;IFERROR(" "&amp;MID(H28,FIND(" ",H28)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H28,FIND(" ",H28,FIND(" ",H28)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C62" s="99"/>
-      <c r="D62" s="99"/>
-      <c r="E62" s="97"/>
-      <c r="F62" s="97"/>
-      <c r="G62" s="97"/>
-      <c r="H62" s="97"/>
-      <c r="I62" s="97"/>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
+      <c r="C68" s="106"/>
+      <c r="D68" s="106"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="104"/>
+      <c r="I68" s="104"/>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="89">
     <mergeCell ref="F10:I10"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
     <mergeCell ref="H29:I29"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="D25:G25"/>
     <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H64:I64"/>
     <mergeCell ref="D28:G28"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="D22:G22"/>
     <mergeCell ref="D23:G23"/>
-    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C41:I41"/>
     <mergeCell ref="D27:G27"/>
     <mergeCell ref="H27:I27"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B53:I54"/>
+    <mergeCell ref="B59:I60"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="E60:G60"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B42:B43"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C42:C43"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D17:I17"/>
@@ -2543,7 +2609,7 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="31" max="8" man="1"/>
+    <brk id="37" max="8" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="9" max="1048575" man="1"/>
@@ -2579,17 +2645,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
       <c r="J1" s="35"/>
       <c r="K1" s="34"/>
       <c r="L1" s="34"/>
@@ -2604,29 +2670,29 @@
       <c r="U1" s="34"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="113" t="s">
+      <c r="A2" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="121"/>
+      <c r="T2" s="121"/>
+      <c r="U2" s="121"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J3" s="2"/>
@@ -2640,23 +2706,23 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117">
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="125">
         <f>' акт заполняем первым'!D16</f>
         <v>0</v>
       </c>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
       <c r="M4" s="32"/>
       <c r="N4" s="32"/>
       <c r="O4" s="32"/>
@@ -2665,11 +2731,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
       <c r="D5" s="6">
         <f>' акт заполняем первым'!F13</f>
         <v>0.4</v>
@@ -2701,57 +2767,57 @@
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:22" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="114" t="s">
+      <c r="A7" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="121"/>
-      <c r="D7" s="114" t="s">
+      <c r="C7" s="129"/>
+      <c r="D7" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="114" t="s">
+      <c r="E7" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="126" t="s">
+      <c r="F7" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="127"/>
-      <c r="H7" s="126" t="s">
+      <c r="G7" s="135"/>
+      <c r="H7" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="127"/>
-      <c r="J7" s="114" t="s">
+      <c r="I7" s="135"/>
+      <c r="J7" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="114" t="s">
+      <c r="K7" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="126" t="s">
+      <c r="L7" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="127"/>
-      <c r="N7" s="120" t="s">
+      <c r="M7" s="135"/>
+      <c r="N7" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="126" t="s">
+      <c r="O7" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="114" t="s">
+      <c r="P7" s="135"/>
+      <c r="Q7" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="R7" s="124" t="s">
+      <c r="R7" s="132" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="5" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
+      <c r="A8" s="123"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
       <c r="F8" s="11" t="s">
         <v>16</v>
       </c>
@@ -2764,30 +2830,30 @@
       <c r="I8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="115"/>
-      <c r="K8" s="115"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
       <c r="L8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N8" s="122"/>
+      <c r="N8" s="130"/>
       <c r="O8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="115"/>
-      <c r="R8" s="125"/>
+      <c r="Q8" s="123"/>
+      <c r="R8" s="133"/>
     </row>
     <row r="9" spans="1:22" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="127"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
       <c r="F9" s="51"/>
@@ -2819,51 +2885,51 @@
       <c r="V9"/>
     </row>
     <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="131"/>
-      <c r="B10" s="131"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
+      <c r="A10" s="139"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="139"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="139"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="139"/>
+      <c r="R10" s="139"/>
     </row>
     <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="129"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
-      <c r="N11" s="129"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="129"/>
-      <c r="R11" s="129"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="132" t="s">
+      <c r="A12" s="140" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="132"/>
-      <c r="C12" s="132"/>
+      <c r="B12" s="140"/>
+      <c r="C12" s="140"/>
       <c r="D12" s="38">
         <f>SUM(N9:N10)/1000</f>
         <v>0</v>
@@ -2905,53 +2971,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="129" t="s">
+      <c r="A14" s="137" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="129"/>
-      <c r="Q14" s="129"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="137"/>
+      <c r="K14" s="137"/>
+      <c r="L14" s="137"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="137"/>
+      <c r="O14" s="137"/>
+      <c r="P14" s="137"/>
+      <c r="Q14" s="137"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="129" t="s">
+      <c r="A15" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="129"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="129"/>
-      <c r="O15" s="129"/>
-      <c r="P15" s="129"/>
-      <c r="Q15" s="129"/>
+      <c r="B15" s="137"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="137"/>
+      <c r="L15" s="137"/>
+      <c r="M15" s="137"/>
+      <c r="N15" s="137"/>
+      <c r="O15" s="137"/>
+      <c r="P15" s="137"/>
+      <c r="Q15" s="137"/>
     </row>
     <row r="16" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="133">
+      <c r="A16" s="141">
         <f>' акт заполняем первым'!G3</f>
         <v>0</v>
       </c>
-      <c r="B16" s="133"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="48" t="str">
         <f>' акт заполняем первым'!B20&amp;" " &amp;' акт заполняем первым'!H20</f>
         <v>Начальник СКС Захаренко Сергей Александрович</v>
@@ -2968,53 +3034,53 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:23" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="130"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="138"/>
+      <c r="L17" s="138"/>
+      <c r="M17" s="138"/>
+      <c r="N17" s="138"/>
+      <c r="O17" s="138"/>
+      <c r="P17" s="138"/>
+      <c r="Q17" s="138"/>
       <c r="R17" s="12"/>
     </row>
     <row r="18" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="129" t="s">
+      <c r="A18" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="129"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="129"/>
-      <c r="O18" s="129"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="137"/>
+      <c r="O18" s="137"/>
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="133">
+      <c r="A19" s="141">
         <f>' акт заполняем первым'!G3</f>
         <v>0</v>
       </c>
-      <c r="B19" s="133"/>
+      <c r="B19" s="141"/>
       <c r="C19" s="48" t="str">
         <f>[1]Список!$B$3&amp;" "&amp;[1]Список!$D$3</f>
         <v>директор Красильников Денис Николаевич</v>
@@ -3034,23 +3100,23 @@
       <c r="W19" s="5"/>
     </row>
     <row r="20" spans="1:23" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="128" t="s">
+      <c r="A20" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="128"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="128"/>
-      <c r="L20" s="128"/>
-      <c r="M20" s="128"/>
-      <c r="N20" s="128"/>
-      <c r="O20" s="128"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="136"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
       <c r="W20" s="5"/>
     </row>
   </sheetData>

--- a/templates/чек-лист_акт_шаблон.xlsx
+++ b/templates/чек-лист_акт_шаблон.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name=" акт заполняем первым" sheetId="2" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t xml:space="preserve">Марка провода (кабеля) </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>АКТ ИНВЕНТАРИЗАЦИИ (ТЕХНИЧЕСКОГО АУДИТА)</t>
   </si>
   <si>
@@ -323,6 +320,10 @@
   <si>
     <t>___</t>
   </si>
+  <si>
+    <t xml:space="preserve">Количество экземпляров оформляется по количеству сторон, участвующих в осмотре объекта
+</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +333,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="[$-FC19]dd\ mmmm\ yyyy\ \г\.;@"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,6 +578,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -762,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -924,51 +932,198 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -984,143 +1139,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1159,36 +1200,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1270,92 +1281,6 @@
               <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:t>Лицевая сторона</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1381124</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Надпись 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1990724" cy="419100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="6350">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="800">
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Количество экземпляров оформляется по количеству сторон, участвующих в осмотре объекта</a:t>
-          </a:r>
-          <a:endParaRPr lang="ru-RU" sz="1000">
-            <a:effectLst/>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="r">
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1000">
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1705,61 +1630,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="B1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="55"/>
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
       <c r="I1" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="B2" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D3" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" s="39"/>
       <c r="F3" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
+        <v>70</v>
+      </c>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="C4" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
+      <c r="C4" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
     </row>
     <row r="5" spans="2:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
+      <c r="B5" s="101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C6" s="15"/>
@@ -1767,36 +1693,36 @@
       <c r="E6" s="15"/>
     </row>
     <row r="7" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="103"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="110"/>
+    </row>
+    <row r="8" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="84"/>
-    </row>
-    <row r="8" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="80" t="s">
+      <c r="C8" s="104"/>
+      <c r="D8" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="80"/>
-      <c r="D8" s="85" t="s">
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="113"/>
+    </row>
+    <row r="9" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="87"/>
-    </row>
-    <row r="9" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="65" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="66"/>
+      <c r="C9" s="106"/>
       <c r="D9" s="43"/>
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
@@ -1805,108 +1731,111 @@
       <c r="I9" s="45"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="56"/>
+      <c r="B10" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="116"/>
       <c r="D10" s="46"/>
       <c r="E10" s="47"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="118"/>
+      <c r="F10" s="56">
+        <f>G3</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="57"/>
     </row>
     <row r="11" spans="2:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="84"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="122"/>
+    </row>
+    <row r="12" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="73"/>
-    </row>
-    <row r="12" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="57" t="s">
+      <c r="C12" s="84"/>
+      <c r="D12" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="74" t="s">
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="100"/>
+    </row>
+    <row r="13" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="76"/>
-    </row>
-    <row r="13" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="89"/>
-      <c r="D13" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="94"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="90"/>
       <c r="F13" s="50">
         <v>0.4</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="27"/>
       <c r="I13" s="28"/>
     </row>
     <row r="14" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="84"/>
+      <c r="D14" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="98" t="s">
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="96"/>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="100"/>
-    </row>
-    <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="101" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="76"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="100"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="67"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="97"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="93"/>
     </row>
     <row r="17" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="55"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="92"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="88"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C18" s="15"/>
@@ -1914,199 +1843,199 @@
       <c r="E18" s="15"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="103" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="103"/>
+      <c r="B19" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="82"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
     </row>
     <row r="20" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="69" t="str">
+      <c r="B20" s="72" t="str">
         <f>IFERROR(IF([1]Список!$B$2=0,"",[1]Список!$B$2),"")</f>
         <v>Начальник СКС</v>
       </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="61" t="str">
+      <c r="C20" s="72"/>
+      <c r="D20" s="65" t="str">
         <f>IFERROR(IF([1]Список!$C$2=0,"",[1]Список!$C$2),"")</f>
         <v>Филиал ПАО «Россети Волга» - «УРС» - «ЦПО»</v>
       </c>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="61" t="str">
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="65" t="str">
         <f>IFERROR(IF([1]Список!$D$2=0,"",[1]Список!$D$2),"")</f>
         <v>Захаренко Сергей Александрович</v>
       </c>
-      <c r="I20" s="62"/>
+      <c r="I20" s="67"/>
     </row>
     <row r="21" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="119" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="63" t="s">
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="64"/>
+      <c r="I21" s="70"/>
     </row>
     <row r="22" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="69" t="str">
+      <c r="B22" s="72" t="str">
         <f>IFERROR(IF([1]Список!$B$5=0,"",[1]Список!$B$5),"")</f>
         <v>Представитель собственника</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="61" t="str">
+      <c r="C22" s="72"/>
+      <c r="D22" s="65" t="str">
         <f>IFERROR(IF([1]Список!$C$5=0,"",[1]Список!$C$5),"")</f>
         <v/>
       </c>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="61" t="str">
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="65" t="str">
         <f>IFERROR(IF([1]Список!$D$5=0,"",[1]Список!$D$5),"")</f>
         <v/>
       </c>
-      <c r="I22" s="62"/>
+      <c r="I22" s="67"/>
     </row>
     <row r="23" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="105"/>
-      <c r="D23" s="63" t="s">
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="59" t="s">
-        <v>43</v>
-      </c>
       <c r="I23" s="60"/>
     </row>
     <row r="24" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="69" t="str">
+      <c r="B24" s="72" t="str">
         <f>IFERROR(IF([1]Список!$B$6=0,"",[1]Список!$B$6),"")</f>
         <v/>
       </c>
-      <c r="C24" s="69"/>
-      <c r="D24" s="61" t="str">
+      <c r="C24" s="72"/>
+      <c r="D24" s="65" t="str">
         <f>IFERROR(IF([1]Список!$C$6=0,"",[1]Список!$C$6),"")</f>
         <v/>
       </c>
-      <c r="E24" s="116"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="61" t="str">
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="65" t="str">
         <f>IFERROR(IF([1]Список!$D$6=0,"",[1]Список!$D$6),"")</f>
         <v/>
       </c>
-      <c r="I24" s="62"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="105" t="s">
+      <c r="B25" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="73"/>
+      <c r="D25" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="105"/>
-      <c r="D25" s="63" t="s">
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="59" t="s">
-        <v>43</v>
-      </c>
       <c r="I25" s="60"/>
     </row>
     <row r="26" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="69" t="str">
+      <c r="B26" s="72" t="str">
         <f>IFERROR(IF([1]Список!$B$7=0,"",[1]Список!$B$7),"")</f>
         <v/>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="61" t="str">
+      <c r="C26" s="72"/>
+      <c r="D26" s="65" t="str">
         <f>IFERROR(IF([1]Список!$C$7=0,"",[1]Список!$C$7),"")</f>
         <v/>
       </c>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="61" t="str">
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="67"/>
+      <c r="H26" s="65" t="str">
         <f>IFERROR(IF([1]Список!$D$7=0,"",[1]Список!$D$7),"")</f>
         <v/>
       </c>
-      <c r="I26" s="62"/>
+      <c r="I26" s="67"/>
     </row>
     <row r="27" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="105" t="s">
+      <c r="B27" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="73"/>
+      <c r="D27" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="105"/>
-      <c r="D27" s="63" t="s">
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="59" t="s">
-        <v>43</v>
-      </c>
       <c r="I27" s="60"/>
     </row>
     <row r="28" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="69" t="str">
+      <c r="B28" s="72" t="str">
         <f>IFERROR(IF([1]Список!$B$8=0,"",[1]Список!$B$8),"")</f>
         <v/>
       </c>
-      <c r="C28" s="69"/>
-      <c r="D28" s="61" t="str">
+      <c r="C28" s="72"/>
+      <c r="D28" s="65" t="str">
         <f>IFERROR(IF([1]Список!$C$8=0,"",[1]Список!$C$8),"")</f>
         <v/>
       </c>
-      <c r="E28" s="116"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="61" t="str">
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="65" t="str">
         <f>IFERROR(IF([1]Список!$D$8=0,"",[1]Список!$D$8),"")</f>
         <v/>
       </c>
-      <c r="I28" s="62"/>
+      <c r="I28" s="67"/>
     </row>
     <row r="29" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="105" t="s">
+      <c r="B29" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="73"/>
+      <c r="D29" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="105"/>
-      <c r="D29" s="63" t="s">
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="59" t="s">
+      <c r="I29" s="60"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="I29" s="60"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="119" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="54"/>
@@ -2178,7 +2107,7 @@
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="I38" s="31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
@@ -2192,62 +2121,62 @@
       <c r="E40" s="18"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C41" s="107" t="s">
+      <c r="C41" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+    </row>
+    <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="107"/>
-      <c r="E41" s="107"/>
-      <c r="F41" s="107"/>
-      <c r="G41" s="107"/>
-      <c r="H41" s="107"/>
-      <c r="I41" s="107"/>
-    </row>
-    <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="104" t="s">
+      <c r="C42" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="104" t="s">
+      <c r="D42" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="109" t="s">
+      <c r="E42" s="75"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="58"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="110"/>
-      <c r="F42" s="111"/>
-      <c r="G42" s="104" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="104" t="s">
-        <v>51</v>
-      </c>
-      <c r="I42" s="104" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="104"/>
-      <c r="C43" s="104"/>
-      <c r="D43" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" s="113"/>
-      <c r="F43" s="114"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
     </row>
     <row r="44" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="19">
         <v>1</v>
       </c>
       <c r="C44" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="40"/>
+      <c r="E44" s="80"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="23" t="s">
         <v>53</v>
-      </c>
-      <c r="D44" s="40"/>
-      <c r="E44" s="142"/>
-      <c r="F44" s="143"/>
-      <c r="G44" s="23" t="s">
-        <v>54</v>
       </c>
       <c r="H44" s="41"/>
       <c r="I44" s="52"/>
@@ -2343,16 +2272,16 @@
       <c r="I53" s="21"/>
     </row>
     <row r="54" spans="2:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="120" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="120"/>
-      <c r="D54" s="120"/>
-      <c r="E54" s="120"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="120"/>
-      <c r="H54" s="120"/>
-      <c r="I54" s="120"/>
+      <c r="B54" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="62"/>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C55" s="17"/>
@@ -2360,56 +2289,56 @@
       <c r="E55" s="17"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="107" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="107"/>
-      <c r="D56" s="107"/>
-      <c r="E56" s="107"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="107"/>
-      <c r="H56" s="107"/>
-      <c r="I56" s="107"/>
+      <c r="B56" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="63"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="108"/>
-      <c r="C57" s="108"/>
-      <c r="D57" s="108"/>
-      <c r="E57" s="108"/>
-      <c r="F57" s="108"/>
-      <c r="G57" s="108"/>
-      <c r="H57" s="108"/>
-      <c r="I57" s="108"/>
+      <c r="B57" s="64"/>
+      <c r="C57" s="64"/>
+      <c r="D57" s="64"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="64"/>
+      <c r="I57" s="64"/>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="108"/>
-      <c r="C58" s="108"/>
-      <c r="D58" s="108"/>
-      <c r="E58" s="108"/>
-      <c r="F58" s="108"/>
-      <c r="G58" s="108"/>
-      <c r="H58" s="108"/>
-      <c r="I58" s="108"/>
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="64"/>
+      <c r="I58" s="64"/>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="108"/>
-      <c r="C59" s="108"/>
-      <c r="D59" s="108"/>
-      <c r="E59" s="108"/>
-      <c r="F59" s="108"/>
-      <c r="G59" s="108"/>
-      <c r="H59" s="108"/>
-      <c r="I59" s="108"/>
+      <c r="B59" s="64"/>
+      <c r="C59" s="64"/>
+      <c r="D59" s="64"/>
+      <c r="E59" s="64"/>
+      <c r="F59" s="64"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="64"/>
+      <c r="I59" s="64"/>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="108"/>
-      <c r="C60" s="108"/>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
+      <c r="B60" s="64"/>
+      <c r="C60" s="64"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="64"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="64"/>
+      <c r="H60" s="64"/>
+      <c r="I60" s="64"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C61" s="17"/>
@@ -2417,97 +2346,97 @@
       <c r="E61" s="17"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="107" t="s">
+      <c r="B62" s="63" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+    </row>
+    <row r="63" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="107"/>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="107"/>
-    </row>
-    <row r="63" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="104" t="s">
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="104"/>
-      <c r="D63" s="104"/>
-      <c r="E63" s="104" t="s">
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="104"/>
-      <c r="G63" s="104"/>
-      <c r="H63" s="104" t="s">
-        <v>60</v>
-      </c>
-      <c r="I63" s="104"/>
+      <c r="I63" s="58"/>
     </row>
     <row r="64" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="106" t="str">
+      <c r="B64" s="71" t="str">
         <f>IFERROR(LEFT(H20,FIND(" ",H20)-1),H20)&amp;IFERROR(" "&amp;MID(H20,FIND(" ",H20)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H20,FIND(" ",H20,FIND(" ",H20)+1)+1,1)&amp;".","")</f>
         <v>Захаренко С. А.</v>
       </c>
-      <c r="C64" s="106"/>
-      <c r="D64" s="106"/>
-      <c r="E64" s="104"/>
-      <c r="F64" s="104"/>
-      <c r="G64" s="104"/>
-      <c r="H64" s="104"/>
-      <c r="I64" s="104"/>
+      <c r="C64" s="71"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="58"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="58"/>
     </row>
     <row r="65" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="106" t="str">
+      <c r="B65" s="71" t="str">
         <f>IFERROR(LEFT(H22,FIND(" ",H22)-1),H22)&amp;IFERROR(" "&amp;MID(H22,FIND(" ",H22)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H22,FIND(" ",H22,FIND(" ",H22)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C65" s="106"/>
-      <c r="D65" s="106"/>
-      <c r="E65" s="104"/>
-      <c r="F65" s="104"/>
-      <c r="G65" s="104"/>
-      <c r="H65" s="104"/>
-      <c r="I65" s="104"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
     </row>
     <row r="66" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="106" t="str">
+      <c r="B66" s="71" t="str">
         <f>IFERROR(LEFT(H24,FIND(" ",H24)-1),H24)&amp;IFERROR(" "&amp;MID(H24,FIND(" ",H24)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H24,FIND(" ",H24,FIND(" ",H24)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C66" s="106"/>
-      <c r="D66" s="106"/>
-      <c r="E66" s="104"/>
-      <c r="F66" s="104"/>
-      <c r="G66" s="104"/>
-      <c r="H66" s="104"/>
-      <c r="I66" s="104"/>
+      <c r="C66" s="71"/>
+      <c r="D66" s="71"/>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="58"/>
     </row>
     <row r="67" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="106" t="str">
+      <c r="B67" s="71" t="str">
         <f>IFERROR(LEFT(H26,FIND(" ",H26)-1),H26)&amp;IFERROR(" "&amp;MID(H26,FIND(" ",H26)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H26,FIND(" ",H26,FIND(" ",H26)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C67" s="106"/>
-      <c r="D67" s="106"/>
-      <c r="E67" s="104"/>
-      <c r="F67" s="104"/>
-      <c r="G67" s="104"/>
-      <c r="H67" s="104"/>
-      <c r="I67" s="104"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="58"/>
     </row>
     <row r="68" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="106" t="str">
+      <c r="B68" s="71" t="str">
         <f>IFERROR(LEFT(H28,FIND(" ",H28)-1),H28)&amp;IFERROR(" "&amp;MID(H28,FIND(" ",H28)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H28,FIND(" ",H28,FIND(" ",H28)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C68" s="106"/>
-      <c r="D68" s="106"/>
-      <c r="E68" s="104"/>
-      <c r="F68" s="104"/>
-      <c r="G68" s="104"/>
-      <c r="H68" s="104"/>
-      <c r="I68" s="104"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="58"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C69" s="17"/>
@@ -2515,80 +2444,7 @@
       <c r="E69" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="C41:I41"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B59:I60"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="E67:G67"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="G3:I3"/>
+  <mergeCells count="90">
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="H25:I25"/>
@@ -2605,6 +2461,80 @@
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B59:I60"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
@@ -2645,17 +2575,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
+      <c r="A1" s="135" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
       <c r="J1" s="35"/>
       <c r="K1" s="34"/>
       <c r="L1" s="34"/>
@@ -2670,29 +2600,29 @@
       <c r="U1" s="34"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="121"/>
-      <c r="T2" s="121"/>
-      <c r="U2" s="121"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="132"/>
+      <c r="U2" s="132"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J3" s="2"/>
@@ -2706,23 +2636,23 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="126" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125">
+      <c r="A4" s="137" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136">
         <f>' акт заполняем первым'!D16</f>
         <v>0</v>
       </c>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
       <c r="M4" s="32"/>
       <c r="N4" s="32"/>
       <c r="O4" s="32"/>
@@ -2731,11 +2661,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="127" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
+      <c r="A5" s="138" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="138"/>
+      <c r="C5" s="138"/>
       <c r="D5" s="6">
         <f>' акт заполняем первым'!F13</f>
         <v>0.4</v>
@@ -2767,57 +2697,57 @@
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:22" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="122" t="s">
+      <c r="A7" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="128" t="s">
+      <c r="B7" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="129"/>
-      <c r="D7" s="122" t="s">
+      <c r="C7" s="140"/>
+      <c r="D7" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="122" t="s">
+      <c r="E7" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="134" t="s">
+      <c r="F7" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="135"/>
-      <c r="H7" s="134" t="s">
+      <c r="G7" s="125"/>
+      <c r="H7" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="135"/>
-      <c r="J7" s="122" t="s">
+      <c r="I7" s="125"/>
+      <c r="J7" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="122" t="s">
+      <c r="K7" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="134" t="s">
+      <c r="L7" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="135"/>
-      <c r="N7" s="128" t="s">
+      <c r="M7" s="125"/>
+      <c r="N7" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="134" t="s">
+      <c r="O7" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="122" t="s">
+      <c r="P7" s="125"/>
+      <c r="Q7" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="R7" s="132" t="s">
+      <c r="R7" s="143" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="5" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="131"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
+      <c r="A8" s="134"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
       <c r="F8" s="11" t="s">
         <v>16</v>
       </c>
@@ -2830,39 +2760,39 @@
       <c r="I8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
+      <c r="J8" s="134"/>
+      <c r="K8" s="134"/>
       <c r="L8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N8" s="130"/>
+      <c r="N8" s="141"/>
       <c r="O8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="133"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="144"/>
     </row>
     <row r="9" spans="1:22" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1</v>
       </c>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="125"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
       <c r="F9" s="51"/>
       <c r="G9" s="51"/>
       <c r="H9" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I9" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -2885,57 +2815,57 @@
       <c r="V9"/>
     </row>
     <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="139"/>
-      <c r="B10" s="139"/>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="139"/>
-      <c r="N10" s="139"/>
-      <c r="O10" s="139"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="139"/>
-      <c r="R10" s="139"/>
+      <c r="A10" s="129"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="129"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="129"/>
+      <c r="P10" s="129"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="129"/>
     </row>
     <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="137"/>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
+      <c r="A11" s="127"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="127"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="140" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="140"/>
-      <c r="C12" s="140"/>
+      <c r="A12" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
       <c r="D12" s="38">
         <f>SUM(N9:N10)/1000</f>
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -2971,53 +2901,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="137" t="s">
+      <c r="A14" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="137"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="137"/>
-      <c r="O14" s="137"/>
-      <c r="P14" s="137"/>
-      <c r="Q14" s="137"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="127"/>
+      <c r="L14" s="127"/>
+      <c r="M14" s="127"/>
+      <c r="N14" s="127"/>
+      <c r="O14" s="127"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="137"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="127"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="127"/>
+      <c r="P15" s="127"/>
+      <c r="Q15" s="127"/>
     </row>
     <row r="16" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="141">
+      <c r="A16" s="131">
         <f>' акт заполняем первым'!G3</f>
         <v>0</v>
       </c>
-      <c r="B16" s="141"/>
+      <c r="B16" s="131"/>
       <c r="C16" s="48" t="str">
         <f>' акт заполняем первым'!B20&amp;" " &amp;' акт заполняем первым'!H20</f>
         <v>Начальник СКС Захаренко Сергей Александрович</v>
@@ -3033,54 +2963,54 @@
       <c r="Q16" s="42"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:23" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="138" t="s">
+    <row r="17" spans="1:23" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="138"/>
-      <c r="O17" s="138"/>
-      <c r="P17" s="138"/>
-      <c r="Q17" s="138"/>
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="128"/>
+      <c r="P17" s="128"/>
+      <c r="Q17" s="128"/>
       <c r="R17" s="12"/>
     </row>
     <row r="18" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="137" t="s">
+      <c r="A18" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="137"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="137"/>
-      <c r="O18" s="137"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="127"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="127"/>
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="141">
+      <c r="A19" s="131">
         <f>' акт заполняем первым'!G3</f>
         <v>0</v>
       </c>
-      <c r="B19" s="141"/>
+      <c r="B19" s="131"/>
       <c r="C19" s="48" t="str">
         <f>[1]Список!$B$3&amp;" "&amp;[1]Список!$D$3</f>
         <v>директор Красильников Денис Николаевич</v>
@@ -3099,43 +3029,28 @@
       <c r="O19" s="2"/>
       <c r="W19" s="5"/>
     </row>
-    <row r="20" spans="1:23" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="136" t="s">
+    <row r="20" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="136"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="136"/>
-      <c r="O20" s="136"/>
+      <c r="B20" s="126"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="126"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="126"/>
+      <c r="K20" s="126"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="126"/>
       <c r="W20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="A15:Q15"/>
-    <mergeCell ref="A17:Q17"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A14:Q14"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A18:O18"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="Q7:Q8"/>
@@ -3152,6 +3067,21 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="N7:N8"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A15:Q15"/>
+    <mergeCell ref="A17:Q17"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A18:O18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.23622047244094491" top="0.23622047244094491" bottom="0.31496062992125984" header="0" footer="0"/>

--- a/templates/чек-лист_акт_шаблон.xlsx
+++ b/templates/чек-лист_акт_шаблон.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name=" акт заполняем первым" sheetId="2" r:id="rId1"/>
@@ -770,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -929,8 +929,203 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -941,208 +1136,46 @@
     <xf numFmtId="14" fontId="28" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1157,50 +1190,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1295,6 +1298,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Список"/>
+      <sheetName val="Параметры"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1321,8 +1325,15 @@
           <cell r="B5" t="str">
             <v>Представитель собственника</v>
           </cell>
+          <cell r="C5" t="str">
+            <v>АО "УльГЭС"</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Красильников Денис Николаевич</v>
+          </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1630,10 +1641,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="55"/>
+      <c r="C1" s="120"/>
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
       <c r="I1" s="31" t="s">
@@ -1641,16 +1652,16 @@
       </c>
     </row>
     <row r="2" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="3" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D3" s="29" t="s">
@@ -1660,32 +1671,32 @@
       <c r="F3" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
     </row>
     <row r="5" spans="2:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C6" s="15"/>
@@ -1693,36 +1704,36 @@
       <c r="E6" s="15"/>
     </row>
     <row r="7" spans="2:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="110"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="85"/>
     </row>
     <row r="8" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="111" t="s">
+      <c r="C8" s="81"/>
+      <c r="D8" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="113"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="88"/>
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="106"/>
+      <c r="C9" s="67"/>
       <c r="D9" s="43"/>
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
@@ -1731,55 +1742,55 @@
       <c r="I9" s="45"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="116"/>
+      <c r="C10" s="57"/>
       <c r="D10" s="46"/>
       <c r="E10" s="47"/>
-      <c r="F10" s="56">
+      <c r="F10" s="121">
         <f>G3</f>
         <v>0</v>
       </c>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="57"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="122"/>
     </row>
     <row r="11" spans="2:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="84"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="122"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
     </row>
     <row r="12" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="123" t="s">
+      <c r="C12" s="59"/>
+      <c r="D12" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="100"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="77"/>
     </row>
     <row r="13" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="89" t="s">
+      <c r="C13" s="90"/>
+      <c r="D13" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="90"/>
+      <c r="E13" s="95"/>
       <c r="F13" s="50">
         <v>0.4</v>
       </c>
@@ -1790,52 +1801,52 @@
       <c r="I13" s="28"/>
     </row>
     <row r="14" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="84"/>
-      <c r="D14" s="94" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="96"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="106"/>
-      <c r="D15" s="97" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="100"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="77"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="93"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="98"/>
     </row>
     <row r="17" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="115"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="87"/>
-      <c r="I17" s="88"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="92"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="93"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C18" s="15"/>
@@ -1843,199 +1854,199 @@
       <c r="E18" s="15"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="82" t="s">
+      <c r="B19" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="82"/>
+      <c r="C19" s="104"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
     </row>
     <row r="20" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="72" t="str">
+      <c r="B20" s="70" t="str">
         <f>IFERROR(IF([1]Список!$B$2=0,"",[1]Список!$B$2),"")</f>
         <v>Начальник СКС</v>
       </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="65" t="str">
+      <c r="C20" s="70"/>
+      <c r="D20" s="62" t="str">
         <f>IFERROR(IF([1]Список!$C$2=0,"",[1]Список!$C$2),"")</f>
         <v>Филиал ПАО «Россети Волга» - «УРС» - «ЦПО»</v>
       </c>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="65" t="str">
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="62" t="str">
         <f>IFERROR(IF([1]Список!$D$2=0,"",[1]Список!$D$2),"")</f>
         <v>Захаренко Сергей Александрович</v>
       </c>
-      <c r="I20" s="67"/>
+      <c r="I20" s="63"/>
     </row>
     <row r="21" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="119"/>
-      <c r="D21" s="68" t="s">
+      <c r="C21" s="71"/>
+      <c r="D21" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="68" t="s">
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="70"/>
+      <c r="I21" s="65"/>
     </row>
     <row r="22" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="72" t="str">
+      <c r="B22" s="70" t="str">
         <f>IFERROR(IF([1]Список!$B$5=0,"",[1]Список!$B$5),"")</f>
         <v>Представитель собственника</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="65" t="str">
+      <c r="C22" s="70"/>
+      <c r="D22" s="62" t="str">
         <f>IFERROR(IF([1]Список!$C$5=0,"",[1]Список!$C$5),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="65" t="str">
+        <v>АО "УльГЭС"</v>
+      </c>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="62" t="str">
         <f>IFERROR(IF([1]Список!$D$5=0,"",[1]Список!$D$5),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="67"/>
+        <v>Красильников Денис Николаевич</v>
+      </c>
+      <c r="I22" s="63"/>
     </row>
     <row r="23" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="68" t="s">
+      <c r="C23" s="106"/>
+      <c r="D23" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="59" t="s">
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="60"/>
+      <c r="I23" s="61"/>
     </row>
     <row r="24" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="72" t="str">
+      <c r="B24" s="70" t="str">
         <f>IFERROR(IF([1]Список!$B$6=0,"",[1]Список!$B$6),"")</f>
         <v/>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="65" t="str">
+      <c r="C24" s="70"/>
+      <c r="D24" s="62" t="str">
         <f>IFERROR(IF([1]Список!$C$6=0,"",[1]Список!$C$6),"")</f>
         <v/>
       </c>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="65" t="str">
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="62" t="str">
         <f>IFERROR(IF([1]Список!$D$6=0,"",[1]Список!$D$6),"")</f>
         <v/>
       </c>
-      <c r="I24" s="67"/>
+      <c r="I24" s="63"/>
     </row>
     <row r="25" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="68" t="s">
+      <c r="C25" s="106"/>
+      <c r="D25" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="59" t="s">
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="I25" s="60"/>
+      <c r="I25" s="61"/>
     </row>
     <row r="26" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="72" t="str">
+      <c r="B26" s="70" t="str">
         <f>IFERROR(IF([1]Список!$B$7=0,"",[1]Список!$B$7),"")</f>
         <v/>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="65" t="str">
+      <c r="C26" s="70"/>
+      <c r="D26" s="62" t="str">
         <f>IFERROR(IF([1]Список!$C$7=0,"",[1]Список!$C$7),"")</f>
         <v/>
       </c>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="65" t="str">
+      <c r="E26" s="118"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="62" t="str">
         <f>IFERROR(IF([1]Список!$D$7=0,"",[1]Список!$D$7),"")</f>
         <v/>
       </c>
-      <c r="I26" s="67"/>
+      <c r="I26" s="63"/>
     </row>
     <row r="27" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="68" t="s">
+      <c r="C27" s="106"/>
+      <c r="D27" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="59" t="s">
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="I27" s="60"/>
+      <c r="I27" s="61"/>
     </row>
     <row r="28" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="72" t="str">
+      <c r="B28" s="70" t="str">
         <f>IFERROR(IF([1]Список!$B$8=0,"",[1]Список!$B$8),"")</f>
         <v/>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="65" t="str">
+      <c r="C28" s="70"/>
+      <c r="D28" s="62" t="str">
         <f>IFERROR(IF([1]Список!$C$8=0,"",[1]Список!$C$8),"")</f>
         <v/>
       </c>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="65" t="str">
+      <c r="E28" s="118"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="62" t="str">
         <f>IFERROR(IF([1]Список!$D$8=0,"",[1]Список!$D$8),"")</f>
         <v/>
       </c>
-      <c r="I28" s="67"/>
+      <c r="I28" s="63"/>
     </row>
     <row r="29" spans="2:9" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="68" t="s">
+      <c r="C29" s="106"/>
+      <c r="D29" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="59" t="s">
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="I29" s="60"/>
+      <c r="I29" s="61"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="123"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="54"/>
@@ -2121,49 +2132,49 @@
       <c r="E40" s="18"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="63"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108"/>
+      <c r="G41" s="108"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="74" t="s">
+      <c r="D42" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="75"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="58" t="s">
+      <c r="E42" s="111"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="H42" s="58" t="s">
+      <c r="H42" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="I42" s="58" t="s">
+      <c r="I42" s="105" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="77" t="s">
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="78"/>
-      <c r="F43" s="79"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="115"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
     </row>
     <row r="44" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="19">
@@ -2173,8 +2184,8 @@
         <v>52</v>
       </c>
       <c r="D44" s="40"/>
-      <c r="E44" s="80"/>
-      <c r="F44" s="81"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="117"/>
       <c r="G44" s="23" t="s">
         <v>53</v>
       </c>
@@ -2272,16 +2283,16 @@
       <c r="I53" s="21"/>
     </row>
     <row r="54" spans="2:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="62" t="s">
+      <c r="B54" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="62"/>
-      <c r="D54" s="62"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="62"/>
-      <c r="G54" s="62"/>
-      <c r="H54" s="62"/>
-      <c r="I54" s="62"/>
+      <c r="C54" s="124"/>
+      <c r="D54" s="124"/>
+      <c r="E54" s="124"/>
+      <c r="F54" s="124"/>
+      <c r="G54" s="124"/>
+      <c r="H54" s="124"/>
+      <c r="I54" s="124"/>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C55" s="17"/>
@@ -2289,56 +2300,56 @@
       <c r="E55" s="17"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="63" t="s">
+      <c r="B56" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="63"/>
-      <c r="I56" s="63"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="108"/>
+      <c r="F56" s="108"/>
+      <c r="G56" s="108"/>
+      <c r="H56" s="108"/>
+      <c r="I56" s="108"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="64"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64"/>
+      <c r="B57" s="109"/>
+      <c r="C57" s="109"/>
+      <c r="D57" s="109"/>
+      <c r="E57" s="109"/>
+      <c r="F57" s="109"/>
+      <c r="G57" s="109"/>
+      <c r="H57" s="109"/>
+      <c r="I57" s="109"/>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
+      <c r="B58" s="109"/>
+      <c r="C58" s="109"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="109"/>
+      <c r="F58" s="109"/>
+      <c r="G58" s="109"/>
+      <c r="H58" s="109"/>
+      <c r="I58" s="109"/>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="64"/>
-      <c r="C59" s="64"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64"/>
-      <c r="F59" s="64"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="64"/>
-      <c r="I59" s="64"/>
+      <c r="B59" s="109"/>
+      <c r="C59" s="109"/>
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="109"/>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="64"/>
-      <c r="C60" s="64"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="64"/>
-      <c r="H60" s="64"/>
-      <c r="I60" s="64"/>
+      <c r="B60" s="109"/>
+      <c r="C60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C61" s="17"/>
@@ -2346,97 +2357,97 @@
       <c r="E61" s="17"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="63"/>
-      <c r="I62" s="63"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
     </row>
     <row r="63" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58" t="s">
+      <c r="C63" s="105"/>
+      <c r="D63" s="105"/>
+      <c r="E63" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58" t="s">
+      <c r="F63" s="105"/>
+      <c r="G63" s="105"/>
+      <c r="H63" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="I63" s="58"/>
+      <c r="I63" s="105"/>
     </row>
     <row r="64" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="71" t="str">
+      <c r="B64" s="107" t="str">
         <f>IFERROR(LEFT(H20,FIND(" ",H20)-1),H20)&amp;IFERROR(" "&amp;MID(H20,FIND(" ",H20)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H20,FIND(" ",H20,FIND(" ",H20)+1)+1,1)&amp;".","")</f>
         <v>Захаренко С. А.</v>
       </c>
-      <c r="C64" s="71"/>
-      <c r="D64" s="71"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
+      <c r="C64" s="107"/>
+      <c r="D64" s="107"/>
+      <c r="E64" s="105"/>
+      <c r="F64" s="105"/>
+      <c r="G64" s="105"/>
+      <c r="H64" s="105"/>
+      <c r="I64" s="105"/>
     </row>
     <row r="65" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="71" t="str">
+      <c r="B65" s="107" t="str">
         <f>IFERROR(LEFT(H22,FIND(" ",H22)-1),H22)&amp;IFERROR(" "&amp;MID(H22,FIND(" ",H22)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H22,FIND(" ",H22,FIND(" ",H22)+1)+1,1)&amp;".","")</f>
-        <v/>
-      </c>
-      <c r="C65" s="71"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
+        <v>Красильников Д. Н.</v>
+      </c>
+      <c r="C65" s="107"/>
+      <c r="D65" s="107"/>
+      <c r="E65" s="105"/>
+      <c r="F65" s="105"/>
+      <c r="G65" s="105"/>
+      <c r="H65" s="105"/>
+      <c r="I65" s="105"/>
     </row>
     <row r="66" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="71" t="str">
+      <c r="B66" s="107" t="str">
         <f>IFERROR(LEFT(H24,FIND(" ",H24)-1),H24)&amp;IFERROR(" "&amp;MID(H24,FIND(" ",H24)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H24,FIND(" ",H24,FIND(" ",H24)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C66" s="71"/>
-      <c r="D66" s="71"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="58"/>
+      <c r="C66" s="107"/>
+      <c r="D66" s="107"/>
+      <c r="E66" s="105"/>
+      <c r="F66" s="105"/>
+      <c r="G66" s="105"/>
+      <c r="H66" s="105"/>
+      <c r="I66" s="105"/>
     </row>
     <row r="67" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="71" t="str">
+      <c r="B67" s="107" t="str">
         <f>IFERROR(LEFT(H26,FIND(" ",H26)-1),H26)&amp;IFERROR(" "&amp;MID(H26,FIND(" ",H26)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H26,FIND(" ",H26,FIND(" ",H26)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
+      <c r="C67" s="107"/>
+      <c r="D67" s="107"/>
+      <c r="E67" s="105"/>
+      <c r="F67" s="105"/>
+      <c r="G67" s="105"/>
+      <c r="H67" s="105"/>
+      <c r="I67" s="105"/>
     </row>
     <row r="68" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="71" t="str">
+      <c r="B68" s="107" t="str">
         <f>IFERROR(LEFT(H28,FIND(" ",H28)-1),H28)&amp;IFERROR(" "&amp;MID(H28,FIND(" ",H28)+1,1)&amp;".","" )&amp;IFERROR(" "&amp;MID(H28,FIND(" ",H28,FIND(" ",H28)+1)+1,1)&amp;".","")</f>
         <v/>
       </c>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="58"/>
+      <c r="C68" s="107"/>
+      <c r="D68" s="107"/>
+      <c r="E68" s="105"/>
+      <c r="F68" s="105"/>
+      <c r="G68" s="105"/>
+      <c r="H68" s="105"/>
+      <c r="I68" s="105"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C69" s="17"/>
@@ -2445,6 +2456,80 @@
     </row>
   </sheetData>
   <mergeCells count="90">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B59:I60"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="H25:I25"/>
@@ -2461,80 +2546,6 @@
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="E67:G67"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B59:I60"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="C41:I41"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
@@ -2575,17 +2586,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="128" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
       <c r="J1" s="35"/>
       <c r="K1" s="34"/>
       <c r="L1" s="34"/>
@@ -2600,29 +2611,29 @@
       <c r="U1" s="34"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="132"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="132"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J3" s="2"/>
@@ -2636,23 +2647,23 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136">
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="145">
         <f>' акт заполняем первым'!D16</f>
         <v>0</v>
       </c>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
       <c r="M4" s="32"/>
       <c r="N4" s="32"/>
       <c r="O4" s="32"/>
@@ -2661,11 +2672,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="138" t="s">
+      <c r="A5" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="138"/>
-      <c r="C5" s="138"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
       <c r="D5" s="6">
         <f>' акт заполняем первым'!F13</f>
         <v>0.4</v>
@@ -2697,57 +2708,57 @@
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:22" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="133" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="133" t="s">
+      <c r="E7" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="124" t="s">
+      <c r="F7" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="125"/>
-      <c r="H7" s="124" t="s">
+      <c r="G7" s="142"/>
+      <c r="H7" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="125"/>
-      <c r="J7" s="133" t="s">
+      <c r="I7" s="142"/>
+      <c r="J7" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="133" t="s">
+      <c r="K7" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="124" t="s">
+      <c r="L7" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="125"/>
-      <c r="N7" s="139" t="s">
+      <c r="M7" s="142"/>
+      <c r="N7" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="124" t="s">
+      <c r="O7" s="141" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="133" t="s">
+      <c r="P7" s="142"/>
+      <c r="Q7" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="R7" s="143" t="s">
+      <c r="R7" s="135" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="5" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="134"/>
-      <c r="B8" s="141"/>
-      <c r="C8" s="142"/>
-      <c r="D8" s="134"/>
-      <c r="E8" s="134"/>
+      <c r="A8" s="127"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
       <c r="F8" s="11" t="s">
         <v>16</v>
       </c>
@@ -2760,30 +2771,30 @@
       <c r="I8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
       <c r="L8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N8" s="141"/>
+      <c r="N8" s="133"/>
       <c r="O8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="144"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="136"/>
     </row>
     <row r="9" spans="1:22" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1</v>
       </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="125"/>
+      <c r="B9" s="141"/>
+      <c r="C9" s="142"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37"/>
       <c r="F9" s="51"/>
@@ -2815,51 +2826,51 @@
       <c r="V9"/>
     </row>
     <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="129"/>
-      <c r="B10" s="129"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="129"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="129"/>
-      <c r="K10" s="129"/>
-      <c r="L10" s="129"/>
-      <c r="M10" s="129"/>
-      <c r="N10" s="129"/>
-      <c r="O10" s="129"/>
-      <c r="P10" s="129"/>
-      <c r="Q10" s="129"/>
-      <c r="R10" s="129"/>
+      <c r="A10" s="140"/>
+      <c r="B10" s="140"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
     </row>
     <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="127"/>
+      <c r="A11" s="138"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
+      <c r="L11" s="138"/>
+      <c r="M11" s="138"/>
+      <c r="N11" s="138"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
+      <c r="Q11" s="138"/>
+      <c r="R11" s="138"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="130" t="s">
+      <c r="A12" s="143" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
+      <c r="B12" s="143"/>
+      <c r="C12" s="143"/>
       <c r="D12" s="38">
         <f>SUM(N9:N10)/1000</f>
         <v>0</v>
@@ -2901,53 +2912,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="127"/>
-      <c r="L14" s="127"/>
-      <c r="M14" s="127"/>
-      <c r="N14" s="127"/>
-      <c r="O14" s="127"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="138"/>
+      <c r="N14" s="138"/>
+      <c r="O14" s="138"/>
+      <c r="P14" s="138"/>
+      <c r="Q14" s="138"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="127"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="127"/>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127"/>
-      <c r="Q15" s="127"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
+      <c r="M15" s="138"/>
+      <c r="N15" s="138"/>
+      <c r="O15" s="138"/>
+      <c r="P15" s="138"/>
+      <c r="Q15" s="138"/>
     </row>
     <row r="16" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="131">
+      <c r="A16" s="144">
         <f>' акт заполняем первым'!G3</f>
         <v>0</v>
       </c>
-      <c r="B16" s="131"/>
+      <c r="B16" s="144"/>
       <c r="C16" s="48" t="str">
         <f>' акт заполняем первым'!B20&amp;" " &amp;' акт заполняем первым'!H20</f>
         <v>Начальник СКС Захаренко Сергей Александрович</v>
@@ -2964,53 +2975,53 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:23" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="128" t="s">
+      <c r="A17" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="128"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="128"/>
-      <c r="P17" s="128"/>
-      <c r="Q17" s="128"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="139"/>
+      <c r="K17" s="139"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="139"/>
+      <c r="N17" s="139"/>
+      <c r="O17" s="139"/>
+      <c r="P17" s="139"/>
+      <c r="Q17" s="139"/>
       <c r="R17" s="12"/>
     </row>
     <row r="18" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="127" t="s">
+      <c r="A18" s="138" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="127"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="127"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="127"/>
-      <c r="O18" s="127"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="138"/>
+      <c r="L18" s="138"/>
+      <c r="M18" s="138"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="138"/>
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="131">
+      <c r="A19" s="144">
         <f>' акт заполняем первым'!G3</f>
         <v>0</v>
       </c>
-      <c r="B19" s="131"/>
+      <c r="B19" s="144"/>
       <c r="C19" s="48" t="str">
         <f>[1]Список!$B$3&amp;" "&amp;[1]Список!$D$3</f>
         <v>директор Красильников Денис Николаевич</v>
@@ -3030,45 +3041,27 @@
       <c r="W19" s="5"/>
     </row>
     <row r="20" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="126"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="126"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
+      <c r="B20" s="137"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="137"/>
+      <c r="O20" s="137"/>
       <c r="W20" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="O7:P7"/>
+  <mergeCells count="29">
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="A20:O20"/>
@@ -3082,6 +3075,22 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="O7:P7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.23622047244094491" top="0.23622047244094491" bottom="0.31496062992125984" header="0" footer="0"/>
